--- a/data/sample_data.xlsx
+++ b/data/sample_data.xlsx
@@ -1,48 +1,174 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+  <si>
+    <t>letter_date</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>nationality</t>
+  </si>
+  <si>
+    <t>passport_no</t>
+  </si>
+  <si>
+    <t>passport_issuing_country</t>
+  </si>
+  <si>
+    <t>date_of_issue</t>
+  </si>
+  <si>
+    <t>date_of_expiry</t>
+  </si>
+  <si>
+    <t>mobile_no</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>date_of_visit</t>
+  </si>
+  <si>
+    <t>pronoun_subj</t>
+  </si>
+  <si>
+    <t>pronoun_subj_cap</t>
+  </si>
+  <si>
+    <t>pronoun_obj</t>
+  </si>
+  <si>
+    <t>pronoun_poss</t>
+  </si>
+  <si>
+    <t>output_filename</t>
+  </si>
+  <si>
+    <t>26 May, 2026</t>
+  </si>
+  <si>
+    <t>Mr. Takamichi Yanai</t>
+  </si>
+  <si>
+    <t>Ms. Hanako Suzuki</t>
+  </si>
+  <si>
+    <t>25/07/1969</t>
+  </si>
+  <si>
+    <t>12/03/1985</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>TS4561348</t>
+  </si>
+  <si>
+    <t>TR9981023</t>
+  </si>
+  <si>
+    <t>18/10/2019</t>
+  </si>
+  <si>
+    <t>01/04/2022</t>
+  </si>
+  <si>
+    <t>18/10/2029</t>
+  </si>
+  <si>
+    <t>01/04/2032</t>
+  </si>
+  <si>
+    <t>+81 90-8501-0521</t>
+  </si>
+  <si>
+    <t>+81 80-1234-5678</t>
+  </si>
+  <si>
+    <t>Adventure, Inc.</t>
+  </si>
+  <si>
+    <t>10th June, 2026</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>He</t>
+  </si>
+  <si>
+    <t>She</t>
+  </si>
+  <si>
+    <t>him</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>his</t>
+  </si>
+  <si>
+    <t>InvitationLetter_Yanai_v2</t>
+  </si>
+  <si>
+    <t>InvitationLetter_Suzuki_v2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDDDDD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,86 +176,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -417,167 +493,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>nationality</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>passport_no</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>passport_issuing_country</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>date_of_issue</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>date_of_expiry</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>mobile_no</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>output_filename</t>
-        </is>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mr. Takamichi Yanai</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>25/07/1969</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TS4561348</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>18/10/2019</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>18/10/2029</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>+81 90-8501-0521</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>InvitationLetter_Yanai</t>
-        </is>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ms. Hanako Suzuki</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>12/03/1985</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TR9981023</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01/04/2022</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>01/04/2032</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>+81 80-1234-5678</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>InvitationLetter_Suzuki</t>
-        </is>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/sample_data.xlsx
+++ b/data/sample_data.xlsx
@@ -1,171 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
-  <si>
-    <t>letter_date</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>nationality</t>
-  </si>
-  <si>
-    <t>passport_no</t>
-  </si>
-  <si>
-    <t>passport_issuing_country</t>
-  </si>
-  <si>
-    <t>date_of_issue</t>
-  </si>
-  <si>
-    <t>date_of_expiry</t>
-  </si>
-  <si>
-    <t>mobile_no</t>
-  </si>
-  <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>date_of_visit</t>
-  </si>
-  <si>
-    <t>pronoun_subj</t>
-  </si>
-  <si>
-    <t>pronoun_subj_cap</t>
-  </si>
-  <si>
-    <t>pronoun_obj</t>
-  </si>
-  <si>
-    <t>pronoun_poss</t>
-  </si>
-  <si>
-    <t>output_filename</t>
-  </si>
-  <si>
-    <t>26 May, 2026</t>
-  </si>
-  <si>
-    <t>Mr. Takamichi Yanai</t>
-  </si>
-  <si>
-    <t>Ms. Hanako Suzuki</t>
-  </si>
-  <si>
-    <t>25/07/1969</t>
-  </si>
-  <si>
-    <t>12/03/1985</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>TS4561348</t>
-  </si>
-  <si>
-    <t>TR9981023</t>
-  </si>
-  <si>
-    <t>18/10/2019</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>18/10/2029</t>
-  </si>
-  <si>
-    <t>01/04/2032</t>
-  </si>
-  <si>
-    <t>+81 90-8501-0521</t>
-  </si>
-  <si>
-    <t>+81 80-1234-5678</t>
-  </si>
-  <si>
-    <t>Adventure, Inc.</t>
-  </si>
-  <si>
-    <t>10th June, 2026</t>
-  </si>
-  <si>
-    <t>he</t>
-  </si>
-  <si>
-    <t>she</t>
-  </si>
-  <si>
-    <t>He</t>
-  </si>
-  <si>
-    <t>She</t>
-  </si>
-  <si>
-    <t>him</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>his</t>
-  </si>
-  <si>
-    <t>InvitationLetter_Yanai_v2</t>
-  </si>
-  <si>
-    <t>InvitationLetter_Suzuki_v2</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="2">
@@ -177,35 +53,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -493,158 +428,340 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>letter_date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>date_of_birth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>passport_no</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>passport_issuing_country</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>date_of_issue</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>date_of_expiry</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mobile_no</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>date_of_visit</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pronoun_subj</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pronoun_subj_cap</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pronoun_obj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pronoun_poss</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>output_filename</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" t="s">
-        <v>39</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>27 May, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mr. Takamichi Yanai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>25/07/1969</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TS4561348</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>18/10/2019</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>18/10/2029</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>+81 90-8501-0521</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Adventure, Inc.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>10th June, 2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>him</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>InvitationLetter_Yanai_v2</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" t="s">
-        <v>40</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>27 May, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ms. Hanako Suzuki</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12/03/1985</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TR9981023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01/04/2022</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01/04/2032</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+81 80-1234-5678</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Adventure, Inc.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10th June, 2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>she</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>She</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>InvitationLetter_Suzuki_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>27 May, 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mr. Ryosuke Kawashima</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2001/04/29</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TT23971111</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2024/04/29</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2034/04/29</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>+81 90-9237-0444</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Adventure, Inc.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11th June, 2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>him</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>InvitationLetter_Kawashima</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/sample_data.xlsx
+++ b/data/sample_data.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,23 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill/>
     </fill>
   </fills>
   <borders count="2">
@@ -57,22 +50,21 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -433,8 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -514,6 +506,11 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>output_filename</t>
         </is>
       </c>
@@ -596,6 +593,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>InvitationLetter_Yanai_v2</t>
         </is>
       </c>
@@ -678,6 +680,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>InvitationLetter_Suzuki_v2</t>
         </is>
       </c>
@@ -760,11 +767,16 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>InvitationLetter_Kawashima</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>